--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92766</v>
+        <v>92772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128651992</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128651996</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128651993</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128652005</v>
       </c>
       <c r="B8" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128651992</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128651996</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128651993</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128652005</v>
       </c>
       <c r="B8" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128651992</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128651996</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128651993</v>
       </c>
       <c r="B7" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128652005</v>
       </c>
       <c r="B8" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91535</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92829</v>
+        <v>92837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652024</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128651992</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128651996</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128652017</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128651993</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128652005</v>
       </c>
       <c r="B8" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128652023</v>
       </c>
       <c r="B9" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128651995</v>
       </c>
       <c r="B10" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8002-2025 artfynd.xlsx
+++ b/artfynd/A 8002-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128652024</v>
+        <v>128652023</v>
       </c>
       <c r="B2" t="n">
-        <v>96265</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>341837</v>
+        <v>341860</v>
       </c>
       <c r="R2" t="n">
-        <v>6576461</v>
+        <v>6576448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128651992</v>
+        <v>128652024</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>341872</v>
+        <v>341837</v>
       </c>
       <c r="R3" t="n">
-        <v>6576427</v>
+        <v>6576461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128651996</v>
+        <v>128652017</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>341890</v>
+        <v>341836</v>
       </c>
       <c r="R4" t="n">
-        <v>6576410</v>
+        <v>6576459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +969,7 @@
         <v>128652022</v>
       </c>
       <c r="B5" t="n">
-        <v>92844</v>
+        <v>93215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128652017</v>
+        <v>128651995</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,7 +1098,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>341836</v>
+        <v>341843</v>
       </c>
       <c r="R6" t="n">
         <v>6576459</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128651993</v>
+        <v>128651996</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341866</v>
+        <v>341890</v>
       </c>
       <c r="R7" t="n">
-        <v>6576453</v>
+        <v>6576410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>128652005</v>
       </c>
       <c r="B8" t="n">
-        <v>58095</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128652023</v>
+        <v>128651992</v>
       </c>
       <c r="B9" t="n">
-        <v>96265</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341860</v>
+        <v>341872</v>
       </c>
       <c r="R9" t="n">
-        <v>6576448</v>
+        <v>6576427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128651995</v>
+        <v>128651993</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341843</v>
+        <v>341866</v>
       </c>
       <c r="R10" t="n">
-        <v>6576459</v>
+        <v>6576453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
